--- a/outputs/matrix_free_elasticity_benchmark.xlsx
+++ b/outputs/matrix_free_elasticity_benchmark.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="matrix_free_benchmark" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'matrix_free_benchmark'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'matrix_free_benchmark'!$A$1:$U$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,17 +446,21 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,72 +481,92 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ncell</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ndof</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nnz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>assembly_time_s</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>assembled_matvec_time_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>matrix_free_matvec_time_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rel_matvec_error</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cg_converged</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cg_iterations</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cg_final_residual</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cg_rel_residual</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matrix_free_solve_time_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>solve_rel_error</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>solution_norm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>assembled_memory_mb</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>matrix_free_memory_est_mb</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>matvec_speedup_vs_numpy</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>solve_speedup_vs_numpy</t>
         </is>
       </c>
     </row>
@@ -560,47 +584,61 @@
           <t>numpy</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>548</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0.001291600001422921</v>
-      </c>
       <c r="H2" s="3" t="n">
-        <v>6.93333398279113e-06</v>
+        <v>0.001554100000248582</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.0003410666661996705</v>
-      </c>
-      <c r="J2" s="4" t="n">
+        <v>3.199999991920777e-06</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.0003202799998689443</v>
+      </c>
+      <c r="K2" s="4" t="n">
         <v>1.576238671987781e-15</v>
       </c>
-      <c r="K2" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>1.454343313134288e-11</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <v>0.01283960000000661</v>
-      </c>
       <c r="O2" s="4" t="n">
-        <v>1.704731280189884e-14</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>0.00836181640625</v>
+        <v>2.980424760299933e-12</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.01223720000052708</v>
       </c>
       <c r="Q2" s="6" t="n">
+        <v>288.3199862781582</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0.012542724609375</v>
+      </c>
+      <c r="S2" s="6" t="n">
         <v>0.0009765625</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -617,47 +655,61 @@
           <t>numpy</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>1988</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.001174900000478374</v>
-      </c>
       <c r="H3" s="3" t="n">
-        <v>6.666666498252501e-06</v>
+        <v>0.001249099999768077</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.0003603666664275806</v>
-      </c>
-      <c r="J3" s="4" t="n">
+        <v>4.500000068219379e-06</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.0003305399999590008</v>
+      </c>
+      <c r="K3" s="4" t="n">
         <v>5.031192789495909e-15</v>
       </c>
-      <c r="K3" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>8.200478325083397e-11</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>0.03696190000118804</v>
-      </c>
       <c r="O3" s="4" t="n">
-        <v>7.787676018635771e-14</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>0.03033447265625</v>
+        <v>9.261617446052029e-12</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.03620370000044204</v>
       </c>
       <c r="Q3" s="6" t="n">
+        <v>1724.372778125806</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>0.045501708984375</v>
+      </c>
+      <c r="S3" s="6" t="n">
         <v>0.00390625</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -674,104 +726,132 @@
           <t>numpy</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>512</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>578</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>7556</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0.003085000000282889</v>
-      </c>
       <c r="H4" s="3" t="n">
-        <v>1.223333432183911e-05</v>
+        <v>0.003161499999805528</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.0006468666676179661</v>
-      </c>
-      <c r="J4" s="4" t="n">
+        <v>9.759999920788687e-06</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.0006138799999462208</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>1.126315883843065e-14</v>
       </c>
-      <c r="K4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>230</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>9.916110413775481e-11</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>0.1409410000014759</v>
-      </c>
       <c r="O4" s="4" t="n">
-        <v>2.949045538972669e-14</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>0.11529541015625</v>
+        <v>5.90899560743537e-12</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.1407890000000407</v>
       </c>
       <c r="Q4" s="6" t="n">
+        <v>11605.5440752417</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0.172943115234375</v>
+      </c>
+      <c r="S4" s="6" t="n">
         <v>0.015625</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3d_n1</t>
+          <t>2d_n32</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>numpy</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>6</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24</v>
+        <v>2048</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.001060099999449449</v>
+        <v>2178</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>29444</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>5.399999887837718e-06</v>
+        <v>0.01176440000017465</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.000676700000137013</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>3.3888343589301e-16</v>
-      </c>
-      <c r="K5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>3.574685570549101e-13</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.008118800000374904</v>
+        <v>3.116000007139519e-05</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.002403559999947902</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>3.273977148614008e-14</v>
+      </c>
+      <c r="L5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>9.445155747364974e-11</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>7.91480416200945e-15</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0.006317138671875</v>
+        <v>2.895129836426204e-12</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.170188700000836</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.0003204345703125</v>
+        <v>84399.25588191477</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0.673919677734375</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -788,51 +868,1201 @@
           <t>numpy</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.001770700000633951</v>
-      </c>
       <c r="H6" s="3" t="n">
-        <v>7.166666667520379e-06</v>
+        <v>0.001943600000231527</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0008016000004621068</v>
-      </c>
-      <c r="J6" s="4" t="n">
+        <v>4.999999873689376e-06</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.0007981400000062422</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>7.901486105999257e-16</v>
       </c>
-      <c r="K6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>2.912618254224969e-11</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>0.04579739999826415</v>
-      </c>
       <c r="O6" s="4" t="n">
-        <v>2.950094706501302e-13</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0.0306243896484375</v>
+        <v>4.828787050197886e-12</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.04642979999971431</v>
       </c>
       <c r="Q6" s="6" t="n">
+        <v>405.1240717660939</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0.04593658447265625</v>
+      </c>
+      <c r="S6" s="6" t="n">
         <v>0.0025634765625</v>
       </c>
+      <c r="T6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3d_n4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>11997</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.01029909999942902</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1.818000000639586e-05</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.00337653999995382</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>2.746180341802418e-15</v>
+      </c>
+      <c r="L7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>9.385753293441004e-11</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>7.046486139906638e-12</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.4845906000000468</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>4882.390200375922</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0.2745895385742188</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0.0205078125</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3d_n8</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3072</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2187</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>81873</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.084808300000077</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.0001174600000013015</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.02370600000012928</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>7.519892926891037e-15</v>
+      </c>
+      <c r="L8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>9.957991327292137e-11</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>3.063783992026916e-12</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>6.980680099999518</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>75318.43980803189</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>1.873924255371094</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0.1640625</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2d_n4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.6415452000001096</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2.451999989716569e-05</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.002452159999847936</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1.675927763300877e-15</v>
+      </c>
+      <c r="L9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>4.261088098734706e-11</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>8.732362132513641e-12</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0.1047838000004049</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>288.3199862781583</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0.012542724609375</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>0.0009765625</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0.1306113793099984</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>0.1167852282555109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2d_n8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.003367899999830115</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>5.787999998574378e-05</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.002608780000082334</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>3.768597385567585e-15</v>
+      </c>
+      <c r="L10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>6.940811573662264e-11</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>7.838950243153837e-12</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.2751853999998275</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>1724.372778125804</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0.045501708984375</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0.00390625</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0.1267029032530796</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0.1315611220670309</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2d_n16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>7556</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.004394999999931315</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.0001268800000616466</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.002495180000005348</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1.270771460362586e-14</v>
+      </c>
+      <c r="L11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>9.859201132190103e-11</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>5.875083450261007e-12</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.644854099999975</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>11605.54407524169</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0.172943115234375</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0.2460263387590895</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0.2183269052643786</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2d_n32</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2178</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>29444</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.007966500000293308</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.0005146800000147778</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.003402219999952649</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>3.376491790205965e-14</v>
+      </c>
+      <c r="L12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>9.001589593447358e-11</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>2.759167906206688e-12</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>1.66754359999959</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>84399.25588191491</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0.673919677734375</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0.7064681296275237</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.7017439903826943</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3d_n2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.005984899999930349</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>4.520000002230518e-05</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.004621399999996357</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>8.9825022837812e-16</v>
+      </c>
+      <c r="L13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>2.043356944932827e-11</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>3.387651485158013e-12</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.3048992000003636</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>405.1240717660937</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0.04593658447265625</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0.0025634765625</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0.1727052408375971</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.1522791794785258</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3d_n4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>11997</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.009312999999565363</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.000184360000093875</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.006608140000025742</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>2.492268604835206e-15</v>
+      </c>
+      <c r="L14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>9.545939244936711e-11</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>7.166747993349029e-12</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.9855383000003712</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>4882.390200375919</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0.2745895385742188</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0.0205078125</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0.5109667773292738</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0.4917014386958521</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3d_n8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3072</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2187</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>81873</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.04594749999978376</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.001234320000003208</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.02013021999991906</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>7.463472340660135e-15</v>
+      </c>
+      <c r="L15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>9.90019694110581e-11</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>3.046002342153273e-12</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>6.440008200000193</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>75318.43980803175</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>1.873924255371094</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0.1640625</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>1.177632435225477</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>1.083955157075624</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2d_n4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.7391351999995095</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.0006660000000920264</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.006546060000073339</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>1.700293251065012e-15</v>
+      </c>
+      <c r="L16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>5.196238714504073e-11</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>1.064879137221091e-11</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.3097292000002199</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>288.3199862781585</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0.012542724609375</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0.0009765625</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0.04892714088556414</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.03950935204210128</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2d_n8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.01845439999942755</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.0004025600001114071</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.005293379999966419</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>4.828568996458189e-15</v>
+      </c>
+      <c r="L17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>7.913864151735127e-11</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>8.937915495636704e-12</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.6262762999995175</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>1724.372778125803</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0.045501708984375</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0.00390625</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0.06244403386136982</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.05780787170210645</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2d_n16</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>7556</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.006378500000209897</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.0005176000000574277</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.004932100000041828</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>1.195168378758742e-14</v>
+      </c>
+      <c r="L18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>9.756935889141421e-11</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>5.8141437423763e-12</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.214885999999751</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>11605.54407524169</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0.172943115234375</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0.1244662516861002</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.1158865934746713</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2d_n32</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2178</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>29444</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.007295000000340224</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.0004269000000931555</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.003996220000044559</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>3.47577997818852e-14</v>
+      </c>
+      <c r="L19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>8.712605946158275e-11</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>2.670588617322086e-12</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.401342000000113</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>84399.25588191491</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0.673919677734375</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0.6014583781476248</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.4873061396505705</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3d_n2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.01911420000033104</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.0004378800000267802</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.02052776000000449</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>7.719377598313609e-16</v>
+      </c>
+      <c r="L20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>3.382880310236771e-11</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>5.608427610019025e-12</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.083138700000745</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>405.1240717660937</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.04593658447265625</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.0025634765625</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.03888100796219693</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.04286597829039102</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3d_n4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>11997</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.0168813999998747</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.0007083000000420725</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.01705629999996745</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>2.845849280201089e-15</v>
+      </c>
+      <c r="L21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>8.835604023030116e-11</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>6.633453846426354e-12</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.769096200000604</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>4882.39020037592</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0.2745895385742188</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0.0205078125</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0.1979643885227314</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.1749995540060837</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3d_n8</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pytorch</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3072</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2187</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>81873</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.01628459999938059</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.0003551599998900201</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.01896169999999984</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>7.880381924687045e-15</v>
+      </c>
+      <c r="L22" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>9.936786919897683e-11</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>3.057260013264503e-12</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>5.996344899999713</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>75318.43980803175</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>1.873924255371094</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>0.1640625</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>1.250204359320603</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>1.164155867685305</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q6"/>
+  <autoFilter ref="A1:U22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>